--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-core-person.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-core-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="152">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,6 +260,10 @@
   </si>
   <si>
     <t>*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PersonFamilyRequired:L'élément name.family pour un professionnel doit être présent au moins une fois pour identifier la personne. {name.item.family.count() = 1}
+</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1029,25 +1033,25 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>80</v>
@@ -1065,11 +1069,11 @@
         <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1096,11 +1100,11 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>74</v>
@@ -1118,7 +1122,7 @@
         <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
@@ -1138,10 +1142,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1164,11 +1168,11 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1219,7 +1223,7 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
@@ -1239,10 +1243,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1265,11 +1269,11 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1320,7 +1324,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -1340,17 +1344,17 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>80</v>
@@ -1368,11 +1372,11 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1399,11 +1403,11 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>74</v>
@@ -1421,7 +1425,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1441,17 +1445,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1469,11 +1473,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1524,7 +1528,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1544,17 +1548,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1572,11 +1576,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1627,7 +1631,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1647,17 +1651,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1675,11 +1679,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1688,7 +1692,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1730,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1750,17 +1754,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1778,11 +1782,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1833,7 +1837,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1853,10 +1857,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1879,11 +1883,11 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1934,7 +1938,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1954,10 +1958,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1968,7 +1972,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -1980,7 +1984,7 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1991,7 +1995,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2009,11 +2013,11 @@
         <v>74</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2031,7 +2035,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2051,10 +2055,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2077,7 +2081,7 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -2088,7 +2092,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2106,11 +2110,11 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2128,7 +2132,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2148,10 +2152,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2174,10 +2178,10 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2229,7 +2233,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2249,10 +2253,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2275,11 +2279,11 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2330,7 +2334,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2350,10 +2354,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2376,11 +2380,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2431,7 +2435,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2451,17 +2455,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>80</v>
@@ -2479,11 +2483,11 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2510,11 +2514,11 @@
         <v>74</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>74</v>
@@ -2532,7 +2536,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2552,10 +2556,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2578,11 +2582,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2633,7 +2637,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2653,10 +2657,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2679,11 +2683,11 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2734,7 +2738,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2754,17 +2758,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -2782,11 +2786,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2813,11 +2817,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -2835,7 +2839,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2855,17 +2859,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>80</v>
@@ -2883,11 +2887,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2938,7 +2942,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -2958,17 +2962,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>80</v>
@@ -2986,11 +2990,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3041,7 +3045,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3061,17 +3065,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>75</v>
@@ -3089,11 +3093,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3102,7 +3106,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>74</v>
@@ -3144,7 +3148,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3164,17 +3168,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>75</v>
@@ -3192,11 +3196,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3247,7 +3251,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3267,10 +3271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3293,11 +3297,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3348,7 +3352,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3368,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3394,7 +3398,7 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -3405,49 +3409,49 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3467,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3493,7 +3497,7 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -3504,7 +3508,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>74</v>
@@ -3546,7 +3550,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3566,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3592,7 +3596,7 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -3645,7 +3649,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-core-person.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-core-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
